--- a/data-raw/data-tidy/tech-yearbook/part08-output/01-patent/03-valid/2023.xlsx
+++ b/data-raw/data-tidy/tech-yearbook/part08-output/01-patent/03-valid/2023.xlsx
@@ -44,25 +44,25 @@
     <t xml:space="preserve">件</t>
   </si>
   <si>
-    <t xml:space="preserve">v4_cg_zlsq2_hj</t>
+    <t xml:space="preserve">v4_cg_zlsyx_hj</t>
   </si>
   <si>
     <t xml:space="preserve">发明</t>
   </si>
   <si>
-    <t xml:space="preserve">v4_cg_zlsq2_fm</t>
+    <t xml:space="preserve">v4_cg_zlsyx_fm</t>
   </si>
   <si>
     <t xml:space="preserve">实用新型</t>
   </si>
   <si>
-    <t xml:space="preserve">v4_cg_zlsq2_syxx</t>
+    <t xml:space="preserve">v4_cg_zlsyx_syxx</t>
   </si>
   <si>
     <t xml:space="preserve">外观设计</t>
   </si>
   <si>
-    <t xml:space="preserve">v4_cg_zlsq2_wgsj</t>
+    <t xml:space="preserve">v4_cg_zlsyx_wgsj</t>
   </si>
   <si>
     <t xml:space="preserve">北京</t>
